--- a/test_data/output_청구서_템플릿.xlsx
+++ b/test_data/output_청구서_템플릿.xlsx
@@ -9,6 +9,14 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="회사별요약" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별실적" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="a" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="회귀_원본데이터" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="회귀_수식복사" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="회귀_수식복사_대상" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="회귀_병합복붙" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="회귀_삽입삭제" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="회귀_중복계수" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="회귀_청구항목" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -85,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -93,6 +101,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -874,6 +886,191 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="2" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>■ 청구항목 합산 테스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>청구항목</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>금액</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>포함대상</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>기대합계</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>기본료</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>37000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>전국대표 포함한 기본료</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>월구전화 기본료는 제외</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>080포함한 기본료</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>월구전화 기본료</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>90000</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>제외해야 함</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>기본료 할인</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>제외해야 함</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>데이터 기본료</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>제외해야 함</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -973,4 +1170,4141 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>■ 회귀 테스트 원본 데이터 (a시트)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>삭제테스트A</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>삭제테스트B</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>조건값</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>회사명</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>중복개수</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>금액</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>청구항목</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>단가</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>합계수식</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>부서</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>담당자</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>삭제대상</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>복사대상</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>우선순위</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>보조일자</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>효력발생인자</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>계약상태</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>지역</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>정렬검증ID</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>당월매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>A삭제1</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>B삭제1</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>ABC통신</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>B2B 데이터(5G)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>검토</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>기본료</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L4" s="3">
+        <f>I4*K4</f>
+        <v/>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>팀1</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>담당1</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>삭제값1</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="n"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>ROW-01</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>A삭제2</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>B삭제2</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>글로벌네트워크</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>B2B 음성</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>전국대표 포함한 기본료</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L5" s="3">
+        <f>I5*K5</f>
+        <v/>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>팀2</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>담당2</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>삭제값2</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>ROW-02</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>A삭제3</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>B삭제3</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>456</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>스마트링크</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>전용회선</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>080포함한 기본료</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L6" s="3">
+        <f>I6*K6</f>
+        <v/>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>팀3</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>담당3</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>삭제값3</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="n"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>ROW-03</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>810000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>A삭제4</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>B삭제4</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>코리아텔레콤</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>검토</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>월구전화 기본료</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>9000</v>
+      </c>
+      <c r="L7" s="3">
+        <f>I7*K7</f>
+        <v/>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>팀4</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>담당4</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>삭제값4</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="n"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>긴급</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>ROW-04</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>A삭제5</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>B삭제5</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>디지털파트너스</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>기업메시지</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>데이터 기본료</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L8" s="3">
+        <f>I8*K8</f>
+        <v/>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>팀1</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>담당5</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>삭제값5</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="n"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>ROW-05</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>760000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>A삭제6</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>B삭제6</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>프라임모바일</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>관제서비스</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>기본료 할인</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>7000</v>
+      </c>
+      <c r="L9" s="3">
+        <f>I9*K9</f>
+        <v/>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>팀2</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>담당6</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>삭제값6</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="n"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>ROW-06</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>A삭제7</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>B삭제7</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>456</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>위즈컴</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>B2B 데이터(5G)</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>검토</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>부가서비스</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L10" s="3">
+        <f>I10*K10</f>
+        <v/>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>팀3</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>담당7</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>삭제값7</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="n"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>ROW-07</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>980000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>A삭제8</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>B삭제8</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>미래통신</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>B2B 음성</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>기본료</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L11" s="3">
+        <f>I11*K11</f>
+        <v/>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>팀4</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>담당8</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>삭제값8</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="n"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>긴급</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>ROW-08</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>210000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>A삭제9</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>B삭제9</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>네오링크</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>전용회선</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>기본료</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L12" s="3">
+        <f>I12*K12</f>
+        <v/>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>팀1</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>담당9</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>삭제값9</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="n"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>ROW-09</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>660000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>A삭제10</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>B삭제10</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>테크커넥트</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>검토</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n">
+        <v>8200</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>전국대표 포함한 기본료</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>9000</v>
+      </c>
+      <c r="L13" s="3">
+        <f>I13*K13</f>
+        <v/>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>팀2</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>담당10</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>삭제값10</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="n"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>ROW-10</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="n">
+        <v>530000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>A삭제11</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>B삭제11</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>오리진네트</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>기업메시지</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n">
+        <v>8200</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>080포함한 기본료</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L14" s="3">
+        <f>I14*K14</f>
+        <v/>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>팀3</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>담당11</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>삭제값11</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="n"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>ROW-11</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>A삭제12</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>B삭제12</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>라이브셀</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>관제서비스</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n">
+        <v>9100</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>월구전화 기본료</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>7000</v>
+      </c>
+      <c r="L15" s="3">
+        <f>I15*K15</f>
+        <v/>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>팀4</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>담당12</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>삭제값12</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="n"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>긴급</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>ROW-12</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>880000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:X1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>■ 회귀 테스트 원본 데이터</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>삭제테스트A</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>삭제테스트B</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>조건값</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>회사명</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>상품</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>중복개수</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>금액</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>청구항목</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>단가</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>합계수식</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>부서</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>담당자</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>삭제대상</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>복사대상</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>우선순위</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>보조일자</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>효력발생인자</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>계약상태</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>지역</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>정렬검증ID</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>당월매출</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>A삭제1</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>B삭제1</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>ABC통신</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>B2B 데이터(5G)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>검토</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>기본료</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L4" s="3">
+        <f>I4*K4</f>
+        <v/>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>팀1</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>담당1</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>삭제값1</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="n"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>ROW-01</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>A삭제2</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>B삭제2</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>글로벌네트워크</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>B2B 음성</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>전국대표 포함한 기본료</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L5" s="3">
+        <f>I5*K5</f>
+        <v/>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>팀2</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>담당2</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>삭제값2</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>ROW-02</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>A삭제3</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>B삭제3</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>456</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>스마트링크</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>전용회선</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>080포함한 기본료</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L6" s="3">
+        <f>I6*K6</f>
+        <v/>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>팀3</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>담당3</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>삭제값3</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="n"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>ROW-03</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>810000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>A삭제4</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>B삭제4</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>코리아텔레콤</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>검토</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>월구전화 기본료</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>9000</v>
+      </c>
+      <c r="L7" s="3">
+        <f>I7*K7</f>
+        <v/>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>팀4</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>담당4</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>삭제값4</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="n"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>긴급</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>ROW-04</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>A삭제5</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>B삭제5</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>디지털파트너스</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>기업메시지</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>데이터 기본료</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L8" s="3">
+        <f>I8*K8</f>
+        <v/>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>팀1</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>담당5</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>삭제값5</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="n"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>ROW-05</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>760000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>A삭제6</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>B삭제6</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>프라임모바일</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>관제서비스</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>기본료 할인</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>7000</v>
+      </c>
+      <c r="L9" s="3">
+        <f>I9*K9</f>
+        <v/>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>팀2</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>담당6</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>삭제값6</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="n"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>ROW-06</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>A삭제7</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>B삭제7</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>456</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>위즈컴</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>B2B 데이터(5G)</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>검토</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>부가서비스</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L10" s="3">
+        <f>I10*K10</f>
+        <v/>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>팀3</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>담당7</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>삭제값7</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="n"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>ROW-07</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>980000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>A삭제8</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>B삭제8</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>미래통신</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>B2B 음성</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>기본료</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L11" s="3">
+        <f>I11*K11</f>
+        <v/>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>팀4</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>담당8</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>삭제값8</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="n"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>긴급</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>ROW-08</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>210000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>A삭제9</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>B삭제9</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>네오링크</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>전용회선</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>기본료</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L12" s="3">
+        <f>I12*K12</f>
+        <v/>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>팀1</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>담당9</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>삭제값9</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="n"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>ROW-09</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>660000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>A삭제10</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>B삭제10</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>테크커넥트</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>검토</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n">
+        <v>8200</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>전국대표 포함한 기본료</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>9000</v>
+      </c>
+      <c r="L13" s="3">
+        <f>I13*K13</f>
+        <v/>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>팀2</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>담당10</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>삭제값10</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="n"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>ROW-10</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="n">
+        <v>530000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>A삭제11</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>B삭제11</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>오리진네트</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>기업메시지</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n">
+        <v>8200</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>080포함한 기본료</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="L14" s="3">
+        <f>I14*K14</f>
+        <v/>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>팀3</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>담당11</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>삭제값11</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="n"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>ROW-11</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>A삭제12</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>B삭제12</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>라이브셀</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>관제서비스</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n">
+        <v>9100</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>월구전화 기본료</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>7000</v>
+      </c>
+      <c r="L15" s="3">
+        <f>I15*K15</f>
+        <v/>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>팀4</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>담당12</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>행 단위 정렬 검증용</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>삭제값12</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="n"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>긴급</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>ROW-12</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>880000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:X1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="2" customWidth="1" min="4" max="4"/>
+    <col width="2" customWidth="1" min="5" max="5"/>
+    <col width="2" customWidth="1" min="6" max="6"/>
+    <col width="2" customWidth="1" min="7" max="7"/>
+    <col width="2" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5">
+        <f>B1+C1</f>
+        <v/>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3">
+        <f>B2+C2</f>
+        <v/>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3">
+        <f>B3+C3</f>
+        <v/>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <f>B4+C4</f>
+        <v/>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <f>B5+C5</f>
+        <v/>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+    </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>■ I:K 수식 표</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>기준값</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>두배수식</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>합계수식</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="I11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" s="3">
+        <f>I11*2</f>
+        <v/>
+      </c>
+      <c r="K11" s="3">
+        <f>SUM(I11:J11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="I12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="J12" s="3">
+        <f>I12*2</f>
+        <v/>
+      </c>
+      <c r="K12" s="3">
+        <f>SUM(I12:J12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="I13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J13" s="3">
+        <f>I13*2</f>
+        <v/>
+      </c>
+      <c r="K13" s="3">
+        <f>SUM(I13:J13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="I14" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="J14" s="3">
+        <f>I14*2</f>
+        <v/>
+      </c>
+      <c r="K14" s="3">
+        <f>SUM(I14:J14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="I15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="J15" s="3">
+        <f>I15*2</f>
+        <v/>
+      </c>
+      <c r="K15" s="3">
+        <f>SUM(I15:J15)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="2" customWidth="1" min="2" max="2"/>
+    <col width="2" customWidth="1" min="3" max="3"/>
+    <col width="2" customWidth="1" min="4" max="4"/>
+    <col width="2" customWidth="1" min="5" max="5"/>
+    <col width="2" customWidth="1" min="6" max="6"/>
+    <col width="2" customWidth="1" min="7" max="7"/>
+    <col width="2" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>■ 수식/서식 복사 대상 시트</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>기준값</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>두배수식</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>합계수식</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="2" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>■ 2026년 4월 병합 셀 복사 원본</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>복붙 대상 영역 H1:M7</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>청구 그룹</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n"/>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>금액 그룹</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="n"/>
+      <c r="E2" s="6" t="n"/>
+      <c r="F2" s="6" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>회사명</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>단가</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>공급가</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>합계수식</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ABC통신</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>기본료</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E4" s="3">
+        <f>C4*D4</f>
+        <v/>
+      </c>
+      <c r="F4" s="3">
+        <f>E4*1.1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>글로벌네트워크</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>전국대표 포함한 기본료</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E5" s="3">
+        <f>C5*D5</f>
+        <v/>
+      </c>
+      <c r="F5" s="3">
+        <f>E5*1.1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>스마트링크</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>080포함한 기본료</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E6" s="3">
+        <f>C6*D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="3">
+        <f>E6*1.1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>코리아텔레콤</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>부가서비스</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E7" s="3">
+        <f>C7*D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="3">
+        <f>E7*1.1</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>■ 삽입/삭제 테스트 시트</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>A값</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>B값</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>C값</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>D값</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>E값</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>F값</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>G값</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>H값</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>I값</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>J열_삽입기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>I1</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>J1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>I2</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>J2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>I3</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>J3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>J4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>I5</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>E6</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>F6</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>H6</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>I6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>J6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>E7</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>G7</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>I7</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>J7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>D8</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>E8</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>F8</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>G8</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>H8</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>I8</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>J8</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>■ H열 금액 중복 개수를 G열에 채우는 테스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>회사명</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>기대값</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>공백1</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>공백2</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>중복개수</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>금액</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>DUP-01</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>ABC통신</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>DUP-02</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>글로벌네트워크</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>DUP-03</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>스마트링크</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>DUP-04</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>코리아텔레콤</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>DUP-05</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>디지털파트너스</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>DUP-06</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>프라임모바일</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>DUP-07</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>위즈컴</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>DUP-08</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>미래통신</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>DUP-09</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>네오링크</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>DUP-10</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>테크커넥트</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>DUP-11</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>오리진네트</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>DUP-12</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>라이브셀</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>